--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484601_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484601_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C. HORTELANO ESCRIBA</t>
+          <t>R. CARRION BALLESTER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5499</v>
+        <v>2.2214</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7281</v>
+        <v>2.4417</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8217</v>
+        <v>-0.2203</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.1449</v>
+        <v>3.1465</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2182</v>
+        <v>2.6244</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9267</v>
+        <v>0.5221</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.4008</v>
+        <v>3.6889</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8138</v>
+        <v>3.6472</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.2146</v>
+        <v>0.0417</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.744</v>
+        <v>-0.5424</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.032</v>
+        <v>-1.0228</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2879</v>
+        <v>0.4804</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.4661</v>
+        <v>-1.6493</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.6651</v>
+        <v>-2.7489</v>
       </c>
       <c r="R2" t="n">
-        <v>2.1991</v>
+        <v>1.0995</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3049</v>
+        <v>-0.5532</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9382</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3667</v>
+        <v>-0.4555</v>
       </c>
       <c r="V2" t="n">
-        <v>2.8559</v>
+        <v>1.2774</v>
       </c>
       <c r="W2" t="n">
-        <v>2.8559</v>
+        <v>1.5993</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. CARRION BALLESTER</t>
+          <t>C. HORTELANO ESCRIBA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5145</v>
+        <v>1.5242</v>
       </c>
       <c r="E3" t="n">
-        <v>1.933</v>
+        <v>-0.48</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4185</v>
+        <v>2.0042</v>
       </c>
       <c r="G3" t="n">
-        <v>3.1465</v>
+        <v>-1.1449</v>
       </c>
       <c r="H3" t="n">
-        <v>2.6244</v>
+        <v>-0.2182</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5221</v>
+        <v>-0.9267</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6889</v>
+        <v>-0.4008</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6472</v>
+        <v>0.8138</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0417</v>
+        <v>-1.2146</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5424</v>
+        <v>-0.744</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0228</v>
+        <v>-1.032</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4804</v>
+        <v>0.2879</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.6493</v>
+        <v>-1.4661</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.7489</v>
+        <v>-3.6651</v>
       </c>
       <c r="R3" t="n">
-        <v>1.0995</v>
+        <v>2.1991</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.26</v>
+        <v>1.2792</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6063</v>
+        <v>0.73</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6536999999999999</v>
+        <v>0.5492</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2774</v>
+        <v>2.8559</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5993</v>
+        <v>2.8559</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. OLID SANGÜESA</t>
+          <t>F. BLASCO MANZANO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3251</v>
+        <v>1.0457</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3251</v>
+        <v>1.7681</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-0.7224</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3251</v>
+        <v>0.8512999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3251</v>
+        <v>3.4605</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>-2.6093</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3251</v>
+        <v>2.4042</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3251</v>
+        <v>4.9168</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-2.5126</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-1.5529</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-1.4563</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-0.09669999999999999</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.8326</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0.7506</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-0.6801</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.945</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. BLASCO MANZANO</t>
+          <t>D. OLID SANGÜESA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.181</v>
+        <v>0.3251</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0121</v>
+        <v>0.3251</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1931</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8512999999999999</v>
+        <v>0.3251</v>
       </c>
       <c r="H5" t="n">
-        <v>3.4605</v>
+        <v>0.3251</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.6093</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4042</v>
+        <v>0.3251</v>
       </c>
       <c r="K5" t="n">
-        <v>4.9168</v>
+        <v>0.3251</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.5126</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5529</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4563</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.09669999999999999</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8326</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.9773</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8265</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.1508</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.945</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1999</v>
+        <v>-0.2606</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.6264</v>
+        <v>-1.3651</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4265</v>
+        <v>1.1045</v>
       </c>
       <c r="G6" t="n">
         <v>-1.1489</v>
@@ -922,13 +922,13 @@
         <v>1.0995</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1714</v>
+        <v>0.1107</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0166</v>
+        <v>0.2779</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1548</v>
+        <v>-0.1673</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3219</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. MEDINA LERMA</t>
+          <t>D. OLID SANGUESA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8428</v>
+        <v>-0.4175</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4221</v>
+        <v>-1.0168</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.2648</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5759</v>
+        <v>-0.7795</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6234</v>
+        <v>-0.3306</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1993</v>
+        <v>-0.4489</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6807</v>
+        <v>-1.1303</v>
       </c>
       <c r="K7" t="n">
-        <v>1.5974</v>
+        <v>-0.4893</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0833</v>
+        <v>-0.641</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.2566</v>
+        <v>0.3508</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9739</v>
+        <v>0.1587</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.2827</v>
+        <v>0.1922</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1833</v>
+        <v>0.3665</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0995</v>
+        <v>0.3665</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1282</v>
+        <v>-0.0045</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6576</v>
+        <v>0.1135</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7858000000000001</v>
+        <v>-0.118</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. OLID SANGUESA</t>
+          <t>R. MEDINA LERMA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.102</v>
+        <v>-1.0072</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5526</v>
+        <v>1.2576</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4507</v>
+        <v>-2.2648</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7795</v>
+        <v>-0.5759</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3306</v>
+        <v>0.6234</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4489</v>
+        <v>-1.1993</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1303</v>
+        <v>1.6807</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4893</v>
+        <v>1.5974</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.641</v>
+        <v>0.0833</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3508</v>
+        <v>-2.2566</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1587</v>
+        <v>-0.9739</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1922</v>
+        <v>-1.2827</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3665</v>
+        <v>0.1833</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3665</v>
+        <v>1.0995</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6889999999999999</v>
+        <v>-0.2926</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4223</v>
+        <v>0.4932</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2667</v>
+        <v>-0.7858000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1186</v>
+        <v>-1.6708</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9127</v>
+        <v>-2.4896</v>
       </c>
       <c r="F9" t="n">
-        <v>0.794</v>
+        <v>0.8188</v>
       </c>
       <c r="G9" t="n">
         <v>-1.7943</v>
@@ -1156,13 +1156,13 @@
         <v>0.3665</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2254</v>
+        <v>0.6733</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1901</v>
+        <v>0.6131</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0354</v>
+        <v>0.0601</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8059</v>
+        <v>-2.1851</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.8367</v>
+        <v>-2.9434</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0308</v>
+        <v>0.7583</v>
       </c>
       <c r="G10" t="n">
         <v>-1.6725</v>
@@ -1234,13 +1234,13 @@
         <v>1.6493</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9502</v>
+        <v>-0.3294</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0098</v>
+        <v>-0.1165</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0596</v>
+        <v>-0.2129</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1765</v>
+        <v>-3.5302</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1885</v>
+        <v>-2.79</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.988</v>
+        <v>-0.7402</v>
       </c>
       <c r="G11" t="n">
         <v>-2.3599</v>
@@ -1312,13 +1312,13 @@
         <v>0.5498</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8062</v>
+        <v>-0.1599</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5324</v>
+        <v>-0.1338</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2738</v>
+        <v>-0.026</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6439</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.1187</v>
+        <v>-6.5493</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3864</v>
+        <v>-3.1391</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.7323</v>
+        <v>-3.4102</v>
       </c>
       <c r="G12" t="n">
         <v>-1.2521</v>
@@ -1390,13 +1390,13 @@
         <v>0.733</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9949</v>
+        <v>-0.4255</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2391</v>
+        <v>0.0083</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7559</v>
+        <v>-0.4338</v>
       </c>
       <c r="V12" t="n">
         <v>-2.8559</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-12.1559</v>
+        <v>-10.5043</v>
       </c>
       <c r="E13" t="n">
-        <v>-10.0829</v>
+        <v>-8.4315</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.073</v>
+        <v>-2.0728</v>
       </c>
       <c r="G13" t="n">
         <v>-6.405100000000001</v>
@@ -1447,7 +1447,7 @@
         <v>8.899699999999998</v>
       </c>
       <c r="L13" t="n">
-        <v>-9.294199999999998</v>
+        <v>-9.2942</v>
       </c>
       <c r="M13" t="n">
         <v>-6.0105</v>
@@ -1456,7 +1456,7 @@
         <v>-6.488</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4773</v>
+        <v>0.4773000000000001</v>
       </c>
       <c r="P13" t="n">
         <v>-4.5815</v>
@@ -1468,13 +1468,13 @@
         <v>10.9953</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.1041</v>
+        <v>-0.4525000000000002</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1660999999999998</v>
+        <v>1.8176</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.2702</v>
+        <v>-2.2701</v>
       </c>
       <c r="V13" t="n">
         <v>0.9347000000000008</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.2682</v>
+        <v>6.3081</v>
       </c>
       <c r="E14" t="n">
-        <v>4.7594</v>
+        <v>3.5094</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5088</v>
+        <v>2.7986</v>
       </c>
       <c r="G14" t="n">
         <v>2.4486</v>
@@ -1546,13 +1546,13 @@
         <v>2.5656</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2149</v>
+        <v>1.2547</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8469</v>
+        <v>0.5969</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3679</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>0.9554</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.9115</v>
+        <v>4.9945</v>
       </c>
       <c r="E15" t="n">
         <v>2.8836</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0279</v>
+        <v>2.1109</v>
       </c>
       <c r="G15" t="n">
         <v>2.4977</v>
@@ -1624,13 +1624,13 @@
         <v>2.1991</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2147</v>
+        <v>0.2977</v>
       </c>
       <c r="T15" t="n">
         <v>-0.2217</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4364</v>
+        <v>0.5194</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. BERMEJO DORRONSORO</t>
+          <t>M. BERENGUER CASCO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.1507</v>
+        <v>3.9482</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4215</v>
+        <v>2.6119</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7292</v>
+        <v>1.3363</v>
       </c>
       <c r="G16" t="n">
-        <v>2.9018</v>
+        <v>3.0102</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1455</v>
+        <v>-1.5135</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7564</v>
+        <v>4.5237</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8566</v>
+        <v>3.3953</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6066</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>0.25</v>
+        <v>3.3059</v>
       </c>
       <c r="M16" t="n">
-        <v>1.0453</v>
+        <v>-0.3851</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4611</v>
+        <v>-1.6029</v>
       </c>
       <c r="O16" t="n">
-        <v>1.5063</v>
+        <v>1.2178</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.733</v>
+        <v>1.0995</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R16" t="n">
-        <v>1.0995</v>
+        <v>2.9321</v>
       </c>
       <c r="S16" t="n">
-        <v>1.9373</v>
+        <v>0.4616</v>
       </c>
       <c r="T16" t="n">
-        <v>2.3975</v>
+        <v>0.0834</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4602</v>
+        <v>0.3782</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9554</v>
+        <v>-0.6231</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.9658</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.9554</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. BERENGUER CASCO</t>
+          <t>J. BERMEJO DORRONSORO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.2873</v>
+        <v>2.3582</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5542</v>
+        <v>1.0753</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7331</v>
+        <v>1.2829</v>
       </c>
       <c r="G17" t="n">
-        <v>3.0102</v>
+        <v>2.9018</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.5135</v>
+        <v>1.1455</v>
       </c>
       <c r="I17" t="n">
-        <v>4.5237</v>
+        <v>1.7564</v>
       </c>
       <c r="J17" t="n">
-        <v>3.3953</v>
+        <v>1.8566</v>
       </c>
       <c r="K17" t="n">
-        <v>0.08939999999999999</v>
+        <v>1.6066</v>
       </c>
       <c r="L17" t="n">
-        <v>3.3059</v>
+        <v>0.25</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3851</v>
+        <v>1.0453</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.6029</v>
+        <v>-0.4611</v>
       </c>
       <c r="O17" t="n">
-        <v>1.2178</v>
+        <v>1.5063</v>
       </c>
       <c r="P17" t="n">
-        <v>1.0995</v>
+        <v>-0.733</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R17" t="n">
-        <v>2.9321</v>
+        <v>1.0995</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1994</v>
+        <v>1.1448</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9743000000000001</v>
+        <v>1.0513</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2251</v>
+        <v>0.0935</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6231</v>
+        <v>-0.9554</v>
       </c>
       <c r="W17" t="n">
-        <v>0.9658</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.5889</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. FRANCH RUIZ</t>
+          <t>J. CARRERAS MUÑOZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2425</v>
+        <v>0.9502</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5947</v>
+        <v>0.9502</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6478</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.0734</v>
+        <v>0.9502</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.7243</v>
+        <v>0.3251</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6509</v>
+        <v>0.6251</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.1451</v>
+        <v>0.9502</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.3474</v>
+        <v>0.3251</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2023</v>
+        <v>0.6251</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9284</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3769</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4486</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5656</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.5656</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.4284</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1509</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2775</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.5889</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. CARRERAS MUÑOZ</t>
+          <t>I. FRANCH RUIZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9502</v>
+        <v>0.8986</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9502</v>
+        <v>0.114</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.7846</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9502</v>
+        <v>-3.0734</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3251</v>
+        <v>-3.7243</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6251</v>
+        <v>0.6509</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9502</v>
+        <v>-2.1451</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3251</v>
+        <v>-2.3474</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6251</v>
+        <v>0.2023</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-0.9284</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-1.3769</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.4486</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.5656</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.5656</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.0845</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.6701</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.4144</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.5889</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="20">
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. DEMBELE CUESTA</t>
+          <t>P. BAENA SANCHEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.8479</v>
+        <v>-0.9907</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.586</v>
+        <v>-2.975</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7381</v>
+        <v>1.9842</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4098</v>
+        <v>0.3027</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1951</v>
+        <v>-0.2139</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2147</v>
+        <v>0.5165999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.2187</v>
+        <v>-0.228</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6194</v>
+        <v>0.2167</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5994</v>
+        <v>-0.4448</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8089</v>
+        <v>0.5308</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4243</v>
+        <v>-0.4306</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3846</v>
+        <v>0.9614</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.733</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1833</v>
+        <v>1.6493</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2949</v>
+        <v>0.128</v>
       </c>
       <c r="T22" t="n">
-        <v>0.549</v>
+        <v>0.0019</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2541</v>
+        <v>0.1261</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. SORIANO ZORIO</t>
+          <t>A. DEMBELE CUESTA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8125</v>
+        <v>-1.1291</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1111</v>
+        <v>-1.9706</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2986</v>
+        <v>0.8415</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.9301</v>
+        <v>-0.4098</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.2442</v>
+        <v>-0.1951</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6859</v>
+        <v>-0.2147</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.7438</v>
+        <v>-1.2187</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.5451</v>
+        <v>-0.6194</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.1987</v>
+        <v>-0.5994</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1863</v>
+        <v>0.8089</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6991000000000001</v>
+        <v>0.4243</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5128</v>
+        <v>0.3846</v>
       </c>
       <c r="P23" t="n">
-        <v>1.0995</v>
+        <v>-0.733</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R23" t="n">
-        <v>1.0995</v>
+        <v>0.1833</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3484</v>
+        <v>0.0138</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3673</v>
+        <v>0.1644</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0188</v>
+        <v>-0.1506</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6335</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.6335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. BAENA SANCHEZ</t>
+          <t>J. SORIANO ZORIO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.6997</v>
+        <v>-1.2996</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.225</v>
+        <v>-1.7265</v>
       </c>
       <c r="F24" t="n">
-        <v>1.5253</v>
+        <v>0.4268</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3027</v>
+        <v>-1.9301</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2139</v>
+        <v>-1.2442</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5165999999999999</v>
+        <v>-0.6859</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.228</v>
+        <v>-1.7438</v>
       </c>
       <c r="K24" t="n">
-        <v>0.2167</v>
+        <v>-0.5451</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.4448</v>
+        <v>-1.1987</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5308</v>
+        <v>-0.1863</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4306</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>0.9614</v>
+        <v>0.5128</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.0995</v>
+        <v>1.0995</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.6493</v>
+        <v>1.0995</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.5809</v>
+        <v>0.1644</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.2481</v>
+        <v>0.0174</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3328</v>
+        <v>0.1471</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3219</v>
+        <v>-0.6335</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.3219</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.5698</v>
+        <v>-2.5937</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.4441</v>
+        <v>-3.6749</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8743</v>
+        <v>1.0812</v>
       </c>
       <c r="G25" t="n">
         <v>-1.5683</v>
@@ -2404,13 +2404,13 @@
         <v>1.2828</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8573</v>
+        <v>0.1188</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8627</v>
+        <v>-0.0935</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0054</v>
+        <v>0.2123</v>
       </c>
       <c r="V25" t="n">
         <v>0.3219</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>12.1558</v>
+        <v>14.72</v>
       </c>
       <c r="E26" t="n">
-        <v>2.0727</v>
+        <v>2.072699999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>10.0831</v>
+        <v>12.647</v>
       </c>
       <c r="G26" t="n">
         <v>6.4049</v>
@@ -2482,13 +2482,13 @@
         <v>15.5768</v>
       </c>
       <c r="S26" t="n">
-        <v>2.104200000000001</v>
+        <v>4.6683</v>
       </c>
       <c r="T26" t="n">
         <v>2.2702</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1662</v>
+        <v>2.3982</v>
       </c>
       <c r="V26" t="n">
         <v>-0.9346999999999999</v>
